--- a/ModExample/Defs/excel_data/物品_合成_蓝图.xlsx
+++ b/ModExample/Defs/excel_data/物品_合成_蓝图.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Territory\数值表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B71DEC7-095C-4707-9B18-93597BD6A4E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A8C500B-397B-4FE7-A5C7-D14754FF67B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="690" windowWidth="28830" windowHeight="15510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40141,7 +40141,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I102 I109 O102:O108 M102:M108">
+  <conditionalFormatting sqref="I109 I102 O102:O108 M102:M108">
     <cfRule type="colorScale" priority="37">
       <colorScale>
         <cfvo type="min"/>
@@ -40199,8 +40199,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O51">
-    <cfRule type="colorScale" priority="18">
+  <conditionalFormatting sqref="O50 O52 M50:M57">
+    <cfRule type="colorScale" priority="71">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -40209,8 +40209,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O52 O50 M50:M57">
-    <cfRule type="colorScale" priority="71">
+  <conditionalFormatting sqref="O51">
+    <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
